--- a/Sources/raw_sales_export_v2.xlsx
+++ b/Sources/raw_sales_export_v2.xlsx
@@ -604,8 +604,6 @@
       <c r="L5" t="n">
         <v>19.99</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>0.08</v>
       </c>
@@ -674,7 +672,6 @@
           <t>249.00</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>€1.500,00</t>
@@ -700,7 +697,6 @@
           <t>2024-02-03</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>CUST-002</t>
@@ -747,11 +743,9 @@
       <c r="M7" t="n">
         <v>0.2</v>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -769,7 +763,6 @@
           <t>2024-02-04</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Soluções Norte</t>
@@ -803,7 +796,6 @@
       <c r="K8" t="n">
         <v>-1</v>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>780</t>
@@ -834,7 +826,6 @@
           <t>02/05/2024</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>CUST-007</t>
@@ -888,8 +879,6 @@
           <t>2,400.00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -912,7 +901,6 @@
           <t>2024-02-06</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>O'Brien &amp; Sons</t>
@@ -923,7 +911,6 @@
           <t>España</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>P-1001</t>
@@ -945,7 +932,6 @@
       <c r="L10" t="n">
         <v>19.99</v>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>780</t>
@@ -961,7 +947,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -974,7 +959,6 @@
           <t>2024-02-07</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>CUST-007</t>
@@ -1028,8 +1012,6 @@
           <t>€1.500,00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D. Haddad</t>
@@ -1166,14 +1148,11 @@
           <t>1,249.00</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>$1,000.00</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -1349,7 +1328,6 @@
           <t>2024-02-11</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>CUST-006</t>
@@ -1393,7 +1371,6 @@
           <t>1,249.00</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>780</t>
@@ -1424,7 +1401,6 @@
           <t>12 Feb 2024</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>CafÃ© Ã–lsson</t>
@@ -1435,7 +1411,6 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>P-1003</t>
@@ -1470,7 +1445,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
           <t>Brian Lee</t>
@@ -1537,7 +1511,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
           <t>C. Mendes</t>
@@ -1555,7 +1528,6 @@
           <t>14 Feb 2024</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>CUST-002</t>
@@ -1602,7 +1574,6 @@
       <c r="M19" t="n">
         <v>0.1</v>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
         <v>0.19</v>
       </c>
@@ -1611,7 +1582,6 @@
           <t>GBP</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1624,7 +1594,6 @@
           <t>2024-02-15</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>O'Brien &amp; Sons</t>
@@ -1635,7 +1604,6 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>P-1010</t>
@@ -1657,9 +1625,6 @@
       <c r="L20" t="n">
         <v>19.99</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>JPY</t>
@@ -1739,7 +1704,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1795,7 +1759,6 @@
       <c r="L22" t="n">
         <v>9.5</v>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>€1.500,00</t>
@@ -1804,8 +1767,6 @@
       <c r="O22" t="n">
         <v>0.08</v>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1869,7 +1830,6 @@
           <t>€1.500,00</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1941,8 +1901,6 @@
           <t>$1,000.00</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1996,12 +1954,9 @@
       <c r="M25" t="n">
         <v>0.1</v>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
         <v>0.08</v>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2059,7 +2014,6 @@
           <t>$19.99</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>€1.500,00</t>
@@ -2068,8 +2022,6 @@
       <c r="O26" t="n">
         <v>0.08</v>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2136,8 +2088,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2206,7 +2156,6 @@
           <t>CAD</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2219,7 +2168,6 @@
           <t>24 Feb 2024</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve"> Café Ölsson </t>
@@ -2256,11 +2204,9 @@
       <c r="M29" t="n">
         <v>0.1</v>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
         <v>0.08</v>
       </c>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -2361,7 +2307,6 @@
           <t>2024-02-26</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>MÃ¼ller GmbH</t>
@@ -2435,7 +2380,6 @@
           <t>27 Feb 2024</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>1007</t>
@@ -2558,11 +2502,9 @@
       <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
         <v>0.19</v>
       </c>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2658,8 +2600,6 @@
           <t>2024-02-03</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Soluções Norte</t>
@@ -2670,7 +2610,6 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>P-1003</t>
@@ -2705,7 +2644,6 @@
       <c r="O35" t="n">
         <v>0.08</v>
       </c>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -2723,7 +2661,6 @@
           <t>4 Feb 2024</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>CUST-005</t>
@@ -2765,11 +2702,9 @@
       <c r="M36" t="n">
         <v>0.2</v>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
           <t>Brian Lee</t>
@@ -2802,7 +2737,6 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>P-1010</t>
@@ -2837,7 +2771,6 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -2855,7 +2788,6 @@
           <t>2024-02-06</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>1001</t>
@@ -2871,7 +2803,6 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>P-1005</t>
@@ -2898,8 +2829,6 @@
           <t>$1,000.00</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -2993,8 +2922,6 @@
           <t>2024-02-08</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve"> Café Ölsson </t>
@@ -3005,7 +2932,6 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>P-1010</t>
@@ -3024,7 +2950,6 @@
       <c r="K40" t="n">
         <v>4</v>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>780</t>
@@ -3033,8 +2958,6 @@
       <c r="O40" t="n">
         <v>0.19</v>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3052,7 +2975,6 @@
           <t>02/09/2024</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Globex Corp</t>
@@ -3091,7 +3013,6 @@
           <t>249.00</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>€1.500,00</t>
@@ -3162,7 +3083,6 @@
           <t>1,249.00</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>$1,000.00</t>
@@ -3178,7 +3098,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3191,8 +3110,6 @@
           <t>02/11/2024</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t xml:space="preserve"> Café Ölsson </t>
@@ -3236,7 +3153,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
         <v>0.08</v>
       </c>
@@ -3323,7 +3239,6 @@
       <c r="O44" t="n">
         <v>0.08</v>
       </c>
-      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
           <t>D. Haddad</t>
@@ -3341,7 +3256,6 @@
           <t>02/13/2024</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>O'Brien &amp; Sons</t>
@@ -3469,7 +3383,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
           <t>D. Haddad</t>
@@ -3535,8 +3448,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>GBP</t>
@@ -3590,15 +3501,11 @@
       <c r="L48" t="n">
         <v>19.99</v>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3649,10 +3556,6 @@
           <t>1,249.00</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -3799,7 +3702,6 @@
       <c r="L51" t="n">
         <v>9.5</v>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>$1,000.00</t>
@@ -3835,7 +3737,6 @@
           <t>02/20/2024</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Globex Corp</t>
@@ -3872,7 +3773,6 @@
       <c r="M52" t="n">
         <v>0.1</v>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
         <v>0.19</v>
       </c>
@@ -3936,7 +3836,6 @@
       <c r="K53" t="n">
         <v>4</v>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>780</t>
@@ -3947,7 +3846,6 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -4021,7 +3919,6 @@
           <t>€1.500,00</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>CAD</t>
@@ -4108,7 +4005,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4121,7 +4017,6 @@
           <t>2024-02-24</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>CUST-006</t>
@@ -4168,11 +4063,9 @@
       <c r="M56" t="n">
         <v>0.2</v>
       </c>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>0.08</v>
       </c>
-      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
           <t>D. Haddad</t>
@@ -4251,7 +4144,6 @@
           <t>8%</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
           <t>C. Mendes</t>
@@ -4269,7 +4161,6 @@
           <t>2024-02-26</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Soluções Norte</t>
@@ -4313,11 +4204,9 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
         <v>0.08</v>
       </c>
-      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
           <t>Brian Lee</t>
@@ -4394,7 +4283,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4455,14 +4343,11 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
